--- a/artfynd/A 18150-2022 artfynd.xlsx
+++ b/artfynd/A 18150-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18150-2022 artfynd.xlsx
+++ b/artfynd/A 18150-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112129067</v>
+        <v>112128589</v>
       </c>
       <c r="B2" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655241</v>
+        <v>655210</v>
       </c>
       <c r="R2" t="n">
-        <v>6675125</v>
+        <v>6675085</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tuff tillvaro nära hyggeskanten.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112129079</v>
+        <v>112128588</v>
       </c>
       <c r="B3" t="n">
-        <v>99028</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,27 +805,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655188</v>
+        <v>655234</v>
       </c>
       <c r="R3" t="n">
-        <v>6675131</v>
+        <v>6675165</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +896,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -920,51 +915,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112129063</v>
+        <v>112128602</v>
       </c>
       <c r="B4" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655225</v>
+        <v>655213</v>
       </c>
       <c r="R4" t="n">
-        <v>6675110</v>
+        <v>6675119</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1007,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tätt med småplantor.</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,15 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112129073</v>
+        <v>107111884</v>
       </c>
       <c r="B5" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,17 +1077,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bengtsängspussen, Upl</t>
+          <t>Långmyren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655180</v>
+        <v>655095</v>
       </c>
       <c r="R5" t="n">
-        <v>6675133</v>
+        <v>6675150</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,22 +1111,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,6 +1125,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1173,15 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112129069</v>
+        <v>112129063</v>
       </c>
       <c r="B6" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1174,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1225,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655168</v>
+        <v>655225</v>
       </c>
       <c r="R6" t="n">
-        <v>6675142</v>
+        <v>6675110</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1260,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1270,7 +1236,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tätt med småplantor.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,15 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112129072</v>
+        <v>112129065</v>
       </c>
       <c r="B7" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1298,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655162</v>
+        <v>655220</v>
       </c>
       <c r="R7" t="n">
-        <v>6675144</v>
+        <v>6675132</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1360,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Djupt nere bland ris och mossa.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,15 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112129065</v>
+        <v>112129067</v>
       </c>
       <c r="B8" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1422,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1473,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655221</v>
+        <v>655241</v>
       </c>
       <c r="R8" t="n">
-        <v>6675131</v>
+        <v>6675124</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1508,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1518,12 +1484,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Djupt nere bland ris och mossa.</t>
+          <t>Tuff tillvaro nära hyggeskanten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,51 +1516,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112128602</v>
+        <v>112129069</v>
       </c>
       <c r="B9" t="n">
-        <v>56606</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1602,10 +1563,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655214</v>
+        <v>655169</v>
       </c>
       <c r="R9" t="n">
-        <v>6675119</v>
+        <v>6675142</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1637,7 +1598,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1647,7 +1608,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,52 +1635,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112128588</v>
+        <v>112129072</v>
       </c>
       <c r="B10" t="n">
-        <v>5160</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1727,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655234</v>
+        <v>655162</v>
       </c>
       <c r="R10" t="n">
-        <v>6675166</v>
+        <v>6675144</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1762,7 +1717,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1772,7 +1727,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,7 +1736,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1797,6 +1751,355 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112129073</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bengtsängspussen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>655180</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6675133</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>115105793</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bengtsängspussen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>655178</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6675101</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112129079</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bengtsängspussen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>655189</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6675131</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18150-2022 artfynd.xlsx
+++ b/artfynd/A 18150-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128589</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128588</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128602</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107111884</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129063</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129065</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1513,6 +1548,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129067</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1632,6 +1672,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129069</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1751,6 +1796,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129072</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1870,6 +1920,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129073</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1989,6 +2044,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115105793</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2100,8 +2160,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129079</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>